--- a/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
+++ b/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy_Example\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3201D224-6B40-44F1-A639-D22628D57480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8C6DD-FCC4-40D3-A887-9E6FDAD946C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,20 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -68,9 +81,6 @@
     <t>benchmark_file_name</t>
   </si>
   <si>
-    <t>SPY</t>
-  </si>
-  <si>
     <t>Benchmark name</t>
   </si>
   <si>
@@ -215,6 +225,9 @@
   </si>
   <si>
     <t>Backtest_Engine</t>
+  </si>
+  <si>
+    <t>KN_US_Equity_Benchmark</t>
   </si>
 </sst>
 </file>
@@ -746,16 +759,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="89.42578125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.7109375" style="17" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="17" customWidth="1"/>
-    <col min="5" max="16384" width="9.42578125" style="17"/>
+    <col min="1" max="1" width="36.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="89.44140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="69.6640625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="17" customWidth="1"/>
+    <col min="5" max="16384" width="9.44140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,230 +779,230 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="B4" s="5">
         <v>42005</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="B5" s="5">
         <v>46129</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="B6" s="18">
         <v>1000000</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="19">
         <v>0.01</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="B8" s="18">
         <v>0.05</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="6" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="B19" s="20">
         <v>8050</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="10"/>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32.4" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
+++ b/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy_Example\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8C6DD-FCC4-40D3-A887-9E6FDAD946C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E5971A-B59B-4CA5-8B82-12B5F52AEC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
     <t>Backtest_Engine</t>
   </si>
   <si>
-    <t>KN_US_Equity_Benchmark</t>
+    <t>SPY</t>
   </si>
 </sst>
 </file>
@@ -759,16 +759,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="89.44140625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.6640625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="17" customWidth="1"/>
-    <col min="5" max="16384" width="9.44140625" style="17"/>
+    <col min="1" max="1" width="36.42578125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="89.42578125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="69.7109375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="17" customWidth="1"/>
+    <col min="5" max="16384" width="9.42578125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -790,7 +790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -801,7 +801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -812,7 +812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -823,7 +823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -834,7 +834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -845,7 +845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -856,7 +856,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -867,7 +867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
@@ -878,7 +878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -889,7 +889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -900,7 +900,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -911,7 +911,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
@@ -922,7 +922,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
@@ -944,7 +944,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
@@ -955,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>41</v>
       </c>
@@ -977,12 +977,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="10"/>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>42</v>
       </c>
@@ -993,12 +993,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="1:3" ht="32.4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.3">
       <c r="A23" s="14"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16" t="s">

--- a/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
+++ b/Investment_Strategy_Example/Config/backtest_engine_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy_Example\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E5971A-B59B-4CA5-8B82-12B5F52AEC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2B22F-CD02-4E55-91C4-214D4CDAAB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
     <t>Backtest_Engine</t>
   </si>
   <si>
-    <t>SPY</t>
+    <t>KN_US_Equity_Benchmark</t>
   </si>
 </sst>
 </file>
